--- a/ig/carecommunication/StructureDefinition-medcom-careCommunication-provenance.xlsx
+++ b/ig/carecommunication/StructureDefinition-medcom-careCommunication-provenance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>5.0.1</t>
+    <t>5.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-29T10:10:10+00:00</t>
+    <t>2026-02-13T11:55:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1985,7 +1985,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>89</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>118</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>143</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>151</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>173</v>
       </c>
@@ -3617,7 +3617,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>193</v>
       </c>
@@ -3736,7 +3736,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>196</v>
       </c>
@@ -4200,7 +4200,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>232</v>
       </c>
@@ -4545,7 +4545,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>240</v>
       </c>
@@ -4896,7 +4896,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>250</v>
       </c>
@@ -5132,7 +5132,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>263</v>
       </c>
@@ -5604,7 +5604,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>290</v>
       </c>
@@ -6308,7 +6308,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>327</v>
       </c>
@@ -7006,7 +7006,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>351</v>
       </c>
@@ -7121,7 +7121,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>359</v>
       </c>
@@ -7470,7 +7470,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>368</v>
       </c>
@@ -7704,7 +7704,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>381</v>
       </c>
@@ -8055,7 +8055,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>398</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>404</v>
       </c>
@@ -8638,7 +8638,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>407</v>
       </c>
@@ -8987,7 +8987,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>411</v>
       </c>
@@ -9221,7 +9221,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>414</v>
       </c>
@@ -9572,7 +9572,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>418</v>
       </c>
@@ -10040,7 +10040,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>424</v>
       </c>
@@ -10155,7 +10155,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>427</v>
       </c>
@@ -10504,7 +10504,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
         <v>431</v>
       </c>
@@ -10738,7 +10738,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>433</v>
       </c>
@@ -11206,12 +11206,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO81">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/ig/carecommunication/StructureDefinition-medcom-careCommunication-provenance.xlsx
+++ b/ig/carecommunication/StructureDefinition-medcom-careCommunication-provenance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>5.0.2</t>
+    <t>5.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T11:55:29+00:00</t>
+    <t>2026-06-03T09:32:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/carecommunication/StructureDefinition-medcom-careCommunication-provenance.xlsx
+++ b/ig/carecommunication/StructureDefinition-medcom-careCommunication-provenance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>5.0.3</t>
+    <t>5.0.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T09:32:39+00:00</t>
+    <t>2026-06-05T08:11:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
